--- a/website.xlsx
+++ b/website.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="75" windowWidth="22935" windowHeight="10500"/>
+    <workbookView xWindow="120" yWindow="75" windowWidth="22935" windowHeight="10500" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="landingpage" sheetId="7" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="59">
   <si>
     <t>About Us</t>
   </si>
@@ -197,6 +197,9 @@
   </si>
   <si>
     <t>.maintitle</t>
+  </si>
+  <si>
+    <t>reqs</t>
   </si>
 </sst>
 </file>
@@ -614,7 +617,7 @@
         <v>28</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1">
@@ -708,7 +711,7 @@
   <hyperlinks>
     <hyperlink ref="H4" location="main_logo_keys!A1" display="main_logo_keys"/>
     <hyperlink ref="D4" location="main_logo!A1" display="main_logo"/>
-    <hyperlink ref="H6" location="footer!A1" display="footer_keys"/>
+    <hyperlink ref="H6" location="footer_keys!A1" display="footer_keys"/>
     <hyperlink ref="D6" location="footer!A1" display="footer"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
